--- a/mapping/SB_DWH/Mapping_FCT_RLOS_APPLICATION.xlsx
+++ b/mapping/SB_DWH/Mapping_FCT_RLOS_APPLICATION.xlsx
@@ -17,7 +17,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="24">
+  <fonts count="26">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -168,6 +168,15 @@
     <font>
       <name val="Times New Roman"/>
       <sz val="12"/>
+    </font>
+    <font>
+      <name val="Times New Roman"/>
+      <b val="1"/>
+      <sz val="12"/>
+    </font>
+    <font>
+      <name val="Times New Roman"/>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="5">
@@ -238,7 +247,7 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="55">
+  <cellXfs count="56">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="12" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -400,6 +409,9 @@
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="23" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -706,7 +718,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E31"/>
+  <dimension ref="A1:E51"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.1640625" defaultRowHeight="16"/>
   <cols>
     <col width="34.33203125" customWidth="1" style="19" min="1" max="1"/>
@@ -743,7 +755,7 @@
       </c>
       <c r="B2" s="19" t="inlineStr">
         <is>
-          <t>Fact bảng hồ sơ tín dụng RLOS, ảnh chụp trạng thái cuối ngày, grain 1 dòng/hồ sơ/ngày</t>
+          <t>Bảng FACT hồ sơ tín dụng RLOS (bán lẻ/cá nhân) — ảnh trạng thái cuối ngày, số tiền/kỳ hạn phê duyệt cuối cùng</t>
         </is>
       </c>
       <c r="E2" s="52" t="inlineStr">
@@ -790,7 +802,7 @@
       <c r="A5" s="13" t="n"/>
       <c r="E5" s="52" t="inlineStr">
         <is>
-          <t>NG_SB_RLOS_APPLICANT_GENERAL AS E2</t>
+          <t>NG_SB_RLOS_APPLICANT_GENERAL AS E</t>
         </is>
       </c>
     </row>
@@ -896,7 +908,7 @@
       </c>
       <c r="E16" s="6" t="n"/>
     </row>
-    <row r="17" ht="30" customHeight="1">
+    <row r="17" ht="45" customHeight="1">
       <c r="A17" s="28" t="inlineStr">
         <is>
           <t>DAYID</t>
@@ -914,7 +926,7 @@
       </c>
       <c r="D17" s="54" t="inlineStr">
         <is>
-          <t>PK — Driving: NG_SB_RLOS_EXTTABLE. Ngày dữ liệu, dạng số YYYYMMDD</t>
+          <t>Ngày dữ liệu, dạng số YYYYMMDD. Ảnh chụp trạng thái cuối ngày (quy trình A2), giữ nguyên grain 1 dòng/hồ sơ/ngày, quy tắc load T-1 như tài liệu gốc.</t>
         </is>
       </c>
       <c r="E17" s="31" t="inlineStr">
@@ -923,7 +935,7 @@
         </is>
       </c>
     </row>
-    <row r="18" ht="30" customHeight="1">
+    <row r="18" ht="15" customHeight="1">
       <c r="A18" s="28" t="inlineStr">
         <is>
           <t>APPLICATION_SK</t>
@@ -936,7 +948,7 @@
       </c>
       <c r="C18" s="26" t="inlineStr">
         <is>
-          <t>Khóa tới hồ sơ tín dụng</t>
+          <t>Khóa hồ sơ tín dụng</t>
         </is>
       </c>
       <c r="D18" s="54" t="inlineStr">
@@ -946,358 +958,679 @@
       </c>
       <c r="E18" s="31" t="inlineStr">
         <is>
-          <t>LEFT JOIN B ON B.WI_NAME = A.WI_NAME AND v_batch_date BETWEEN B.EFF_DATE AND NVL(B.EXP_DATE, v_batch_date) → B.DIMENSION_KEY</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="90" customHeight="1">
+          <t>B.DIMENSION_KEY</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="45" customHeight="1">
       <c r="A19" s="28" t="inlineStr">
         <is>
+          <t>WI_NAME</t>
+        </is>
+      </c>
+      <c r="B19" s="25" t="inlineStr">
+        <is>
+          <t>VARCHAR2(100)</t>
+        </is>
+      </c>
+      <c r="C19" s="26" t="inlineStr">
+        <is>
+          <t>Mã hồ sơ tín dụng</t>
+        </is>
+      </c>
+      <c r="D19" s="54" t="inlineStr">
+        <is>
+          <t>Mã hồ sơ tín dụng RLOS — nguồn A.WI_NAME. Đổi driving table từ NG_SB_RLOS_ENTRY_EXIT sang NG_SB_RLOS_EXTTABLE (đồng bộ pattern CLOS).</t>
+        </is>
+      </c>
+      <c r="E19" s="31" t="inlineStr">
+        <is>
+          <t>A.WI_NAME</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="120" customHeight="1">
+      <c r="A20" s="28" t="inlineStr">
+        <is>
           <t>WORKSTEP_DECISION_SK</t>
         </is>
       </c>
-      <c r="B19" s="25" t="inlineStr">
+      <c r="B20" s="25" t="inlineStr">
         <is>
           <t>NUMBER</t>
         </is>
       </c>
-      <c r="C19" s="26" t="inlineStr">
-        <is>
-          <t>Khóa tới bước xử lý - quyết định gần nhất</t>
-        </is>
-      </c>
-      <c r="D19" s="54" t="inlineStr">
-        <is>
-          <t>Khóa tới DIM_RLOS_WORKSTEP_DECISION (gộp từ LAST_WORKSTEP_SK+LAST_DECISION_SK) của sự kiện hoàn tất gần nhất, lookup theo cặp WORKSTEP_CODE+DECISION_CODE của sự kiện đó. Mặc định -1</t>
-        </is>
-      </c>
-      <c r="E19" s="31" t="inlineStr">
-        <is>
-          <t>LEFT JOIN (SELECT C2.WORKSTEP, C2.DECISION FROM C C2 WHERE C2.WINAME = A.WI_NAME AND C2.EXITDATE IS NOT NULL AND C2.ENTRYDATE &lt;= v_batch_date ORDER BY C2.ENTRYDATE DESC FETCH FIRST 1 ROW ONLY) LAST_EVENT ON 1=1 → LEFT JOIN D ON D.WORKSTEP_CODE = LAST_EVENT.WORKSTEP AND D.DECISION_CODE = LAST_EVENT.DECISION AND v_batch_date BETWEEN D.EFF_DATE AND NVL(D.EXP_DATE, v_batch_date) → D.DIMENSION_KEY</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="105" customHeight="1">
-      <c r="A20" s="28" t="inlineStr">
+      <c r="C20" s="26" t="inlineStr">
+        <is>
+          <t>Khóa bước &amp; quyết định cuối</t>
+        </is>
+      </c>
+      <c r="D20" s="54" t="inlineStr">
+        <is>
+          <t>Khóa tới DIM_RLOS_WORKSTEP_DECISION (gộp từ LAST_WORKSTEP_SK+LAST_DECISION_SK) của sự kiện hoàn tất gần nhất, lookup theo cặp WORKSTEP_CODE+DECISION_CODE của sự kiện đó. Mặc định -1 — đổi tên từ LAST_WORKSTEP_DECISION_SK. Lookup theo cặp WORKSTEP_CODE+DECISION_CODE của sự kiện hoàn tất gần nhất (LAST_EVENT = dòng có ENTRYDATE lớn nhất, EXITDATE IS NOT NULL, tính đến v_batch_date).</t>
+        </is>
+      </c>
+      <c r="E20" s="31" t="inlineStr">
+        <is>
+          <t>D.DIMENSION_KEY</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="60" customHeight="1">
+      <c r="A21" s="28" t="inlineStr">
+        <is>
+          <t>WORKSTEP_CODE</t>
+        </is>
+      </c>
+      <c r="B21" s="25" t="inlineStr">
+        <is>
+          <t>VARCHAR2(200)</t>
+        </is>
+      </c>
+      <c r="C21" s="26" t="inlineStr">
+        <is>
+          <t>Mã bước xử lý cuối</t>
+        </is>
+      </c>
+      <c r="D21" s="54" t="inlineStr">
+        <is>
+          <t>CỘT MỚI — BK cạnh SK: 1 phần BK composite (WORKSTEP_CODE+DECISION_CODE) của DIM_RLOS_WORKSTEP_DECISION ứng với dòng đã khớp WORKSTEP_DECISION_SK</t>
+        </is>
+      </c>
+      <c r="E21" s="31" t="inlineStr">
+        <is>
+          <t>LAST_EVENT.WORKSTEP</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="45" customHeight="1">
+      <c r="A22" s="28" t="inlineStr">
+        <is>
+          <t>DECISION_CODE</t>
+        </is>
+      </c>
+      <c r="B22" s="25" t="inlineStr">
+        <is>
+          <t>VARCHAR2(200)</t>
+        </is>
+      </c>
+      <c r="C22" s="26" t="inlineStr">
+        <is>
+          <t>Mã quyết định cuối</t>
+        </is>
+      </c>
+      <c r="D22" s="54" t="inlineStr">
+        <is>
+          <t>CỘT MỚI — BK cạnh SK: nửa còn lại BK composite DIM_RLOS_WORKSTEP_DECISION ứng với dòng đã khớp WORKSTEP_DECISION_SK</t>
+        </is>
+      </c>
+      <c r="E22" s="31" t="inlineStr">
+        <is>
+          <t>LAST_EVENT.DECISION</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="120" customHeight="1">
+      <c r="A23" s="28" t="inlineStr">
         <is>
           <t>SUB_PRODUCT_SK</t>
         </is>
       </c>
-      <c r="B20" s="25" t="inlineStr">
+      <c r="B23" s="25" t="inlineStr">
         <is>
           <t>NUMBER</t>
         </is>
       </c>
-      <c r="C20" s="26" t="inlineStr">
-        <is>
-          <t>Khóa tới sản phẩm vay chi tiết</t>
-        </is>
-      </c>
-      <c r="D20" s="54" t="inlineStr">
-        <is>
-          <t>Khóa tới DIM_RLOS_PRODUCT (layer Sub Product) — PHÁI SINH: lookup theo PRODUCTLINE_CODE=NG_SB_RLOS_APPLICANT_GENERAL.PRODUCT_LINE AND SUB_PRODUCT_NAME=NG_SB_RLOS_APPLICANT_GENERAL.SUB_PRODUCT, điều kiện SCD2 EFF_DATE&lt;=DAYID&lt;EXP_DATE (hoặc EXP_DATE IS NULL) trên DIM_RLOS_PRODUCT. Mặc định -1 nếu không khớp</t>
-        </is>
-      </c>
-      <c r="E20" s="31" t="inlineStr">
-        <is>
-          <t>LEFT JOIN E2 ON E2.WI_NAME = A.WI_NAME → LEFT JOIN F ON F.PRODUCTLINE_CODE = E2.PRODUCT_LINE AND F.SUB_PRODUCT_NAME = E2.SUB_PRODUCT AND v_batch_date BETWEEN F.EFF_DATE AND NVL(F.EXP_DATE, v_batch_date) → F.SUB_PRODUCT_SK</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="90" customHeight="1">
-      <c r="A21" s="28" t="inlineStr">
+      <c r="C23" s="26" t="inlineStr">
+        <is>
+          <t>Khóa sản phẩm nhánh</t>
+        </is>
+      </c>
+      <c r="D23" s="54" t="inlineStr">
+        <is>
+          <t>Khóa tới DIM_RLOS_PRODUCT (layer Sub Product) — PHÁI SINH: lookup theo PRODUCTLINE_CODE=E.PRODUCT_LINE AND SUB_PRODUCT_NAME=E.SUB_PRODUCT, điều kiện SCD2 EFF_DATE&lt;=DAYID&lt;EXP_DATE (hoặc EXP_DATE IS NULL) trên DIM_RLOS_PRODUCT. Mặc định -1 nếu không khớp. E.PRODUCT_LINE/SUB_PRODUCT đã xác nhận tồn tại thật (RLOS - Metadata.xlsx). Tên cột nguồn chuẩn là PRODUCTLINE_CODE (không phải PRODUCT_LINE_CODE).</t>
+        </is>
+      </c>
+      <c r="E23" s="31" t="inlineStr">
+        <is>
+          <t>F.SUB_PRODUCT_SK</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="45" customHeight="1">
+      <c r="A24" s="28" t="inlineStr">
+        <is>
+          <t>SUB_PRODUCT_CODE</t>
+        </is>
+      </c>
+      <c r="B24" s="25" t="inlineStr">
+        <is>
+          <t>VARCHAR2(100)</t>
+        </is>
+      </c>
+      <c r="C24" s="26" t="inlineStr">
+        <is>
+          <t>Mã sản phẩm nhánh</t>
+        </is>
+      </c>
+      <c r="D24" s="54" t="inlineStr">
+        <is>
+          <t>CỘT MỚI — BK cạnh SK: Mã sản phẩm nhánh (BK thật của DIM_RLOS_PRODUCT layer Sub Product — khác SUB_PRODUCT_NAME dùng làm điều kiện JOIN)</t>
+        </is>
+      </c>
+      <c r="E24" s="31" t="inlineStr">
+        <is>
+          <t>F.SUB_PRODUCT_CODE</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="135" customHeight="1">
+      <c r="A25" s="28" t="inlineStr">
         <is>
           <t>COMPANY_SK</t>
         </is>
       </c>
-      <c r="B21" s="25" t="inlineStr">
+      <c r="B25" s="25" t="inlineStr">
         <is>
           <t>NUMBER</t>
         </is>
       </c>
-      <c r="C21" s="26" t="inlineStr">
-        <is>
-          <t>Khóa tới công ty/tổ chức</t>
-        </is>
-      </c>
-      <c r="D21" s="54" t="inlineStr">
-        <is>
-          <t>Khóa tới DIM_LOS_COMPANY — PHÁI SINH: lookup theo COMPANY_CODE=NG_SB_RLOS_APPLICANT_GENERAL.COMPANY_CODE, điều kiện SCD2 COMPANY_EFF_DATE&lt;=DAYID&lt;COMPANY_EXP_DATE (hoặc COMPANY_EXP_DATE IS NULL) theo layer Company trên DIM_LOS_COMPANY. Mặc định -1 nếu không khớp</t>
-        </is>
-      </c>
-      <c r="E21" s="31" t="inlineStr">
-        <is>
-          <t>LEFT JOIN E2 ON E2.WI_NAME = A.WI_NAME → LEFT JOIN G ON G.COMPANY_CODE = E2.COMPANY_CODE AND v_batch_date BETWEEN G.COMPANY_EFF_DATE AND NVL(G.COMPANY_EXP_DATE, v_batch_date) → G.DIMENSION_KEY</t>
-        </is>
-      </c>
-    </row>
-    <row r="22" ht="60" customHeight="1">
-      <c r="A22" s="28" t="inlineStr">
-        <is>
-          <t>CHANGE_TYPE_SK</t>
-        </is>
-      </c>
-      <c r="B22" s="25" t="inlineStr">
-        <is>
-          <t>NUMBER</t>
-        </is>
-      </c>
-      <c r="C22" s="26" t="inlineStr">
-        <is>
-          <t>Khóa tới loại thay đổi điều kiện phê duyệt</t>
-        </is>
-      </c>
-      <c r="D22" s="54" t="inlineStr">
-        <is>
-          <t>Khóa tới DIM_RLOS_CHANGE_TYPE. Chỉ có giá trị với hồ sơ thay đổi điều kiện phê duyệt, còn lại Unknown -1. Nguồn: NG_SB_RLOS_EXTTABLE.CHANGE_TYPE</t>
-        </is>
-      </c>
-      <c r="E22" s="31" t="inlineStr">
-        <is>
-          <t>LEFT JOIN H ON H.WI_NAME = A.WI_NAME → LEFT JOIN I ON I.CHANGE_TYPE_CODE = H.CHANGE_TYPE_CODE AND I.DETAIL_CHANGE_TYPE_CODE = H.DETAIL_CHANGE_TYPE_CODE → I.DIMENSION_KEY</t>
-        </is>
-      </c>
-    </row>
-    <row r="23" ht="30" customHeight="1">
-      <c r="A23" s="28" t="inlineStr">
-        <is>
-          <t>CARD_PROMOTION_SK</t>
-        </is>
-      </c>
-      <c r="B23" s="25" t="inlineStr">
-        <is>
-          <t>NUMBER</t>
-        </is>
-      </c>
-      <c r="C23" s="26" t="inlineStr">
-        <is>
-          <t>Khóa tới khuyến mãi thẻ</t>
-        </is>
-      </c>
-      <c r="D23" s="54" t="inlineStr">
-        <is>
-          <t>Khóa tới DIM_RLOS_CARD_PROMOTION. Lookup NG_SB_RLOS_CBS.PROMOTION_ID; hồ sơ không phải thẻ dùng -1</t>
-        </is>
-      </c>
-      <c r="E23" s="31" t="inlineStr">
-        <is>
-          <t>LEFT JOIN J ON J.WI_NAME = A.WI_NAME → LEFT JOIN K ON K.PROMOTION_CODE = J.PROMOTION_ID → K.DIMENSION_KEY</t>
-        </is>
-      </c>
-    </row>
-    <row r="24" ht="30" customHeight="1">
-      <c r="A24" s="28" t="inlineStr">
-        <is>
-          <t>WI_NAME</t>
-        </is>
-      </c>
-      <c r="B24" s="25" t="inlineStr">
-        <is>
-          <t>VARCHAR2(100)</t>
-        </is>
-      </c>
-      <c r="C24" s="26" t="inlineStr">
-        <is>
-          <t>Mã hồ sơ tín dụng</t>
-        </is>
-      </c>
-      <c r="D24" s="54" t="inlineStr">
-        <is>
-          <t>Mã hồ sơ tín dụng RLOS — nguồn NG_SB_RLOS_EXTTABLE.WI_NAME</t>
-        </is>
-      </c>
-      <c r="E24" s="31" t="inlineStr">
-        <is>
-          <t>A.WI_NAME</t>
-        </is>
-      </c>
-    </row>
-    <row r="25" ht="105" customHeight="1">
-      <c r="A25" s="28" t="inlineStr">
-        <is>
-          <t>PROCESSED_DATE</t>
-        </is>
-      </c>
-      <c r="B25" s="25" t="inlineStr">
-        <is>
-          <t>DATE</t>
-        </is>
-      </c>
       <c r="C25" s="26" t="inlineStr">
         <is>
-          <t>Ngày xử lý</t>
+          <t>Khóa đơn vị kinh doanh</t>
         </is>
       </c>
       <c r="D25" s="54" t="inlineStr">
         <is>
-          <t>Ngày xử lý chung của hồ sơ theo 3 mức ưu tiên (phê duyệt cuối / hủy / hoàn tất gần nhất) — nguồn NG_SB_RLOS_ENTRY_EXIT</t>
+          <t>Khóa tới DIM_LOS_COMPANY — PHÁI SINH: lookup theo COMPANY_CODE=E.COMPANY_CODE, điều kiện SCD2 COMPANY_EFF_DATE&lt;=DAYID&lt;COMPANY_EXP_DATE (hoặc COMPANY_EXP_DATE IS NULL) theo layer Company trên DIM_LOS_COMPANY. Mặc định -1 nếu không khớp. Thay thế ORG_UNIT_SK cũ. Lookup theo layer Company (COMPANY_EFF_DATE/COMPANY_EXP_DATE), thay cho EFF_DATE/EXP_DATE chung cũ — DIM_LOS_COMPANY tách 3 layer SCD2 độc lập.</t>
         </is>
       </c>
       <c r="E25" s="31" t="inlineStr">
         <is>
-          <t>COALESCE((SELECT MAX(C2.EXITDATE) FROM C C2 WHERE C2.WINAME = A.WI_NAME AND C2.WORKSTEP IN ('CreditCommittee','CreditApproval') AND C2.DECISION IN ('Send To HOSupport','Reject','Submit','Send To PostSanction','Submit To DisbursementMaker')), (SELECT NVL(C2.EXITDATE, C2.ENTRYDATE) FROM C C2 WHERE C2.WINAME = A.WI_NAME AND C2.WORKSTEP = 'CancelRevoke'), (SELECT C2.EXITDATE FROM C C2 WHERE C2.WINAME = A.WI_NAME AND C2.EXITDATE IS NOT NULL ORDER BY C2.ENTRYDATE DESC FETCH FIRST 1 ROW ONLY))</t>
+          <t>G.DIMENSION_KEY</t>
         </is>
       </c>
     </row>
     <row r="26" ht="30" customHeight="1">
       <c r="A26" s="28" t="inlineStr">
         <is>
-          <t>CREATION_DATE</t>
+          <t>COMPANY_CODE</t>
         </is>
       </c>
       <c r="B26" s="25" t="inlineStr">
         <is>
-          <t>DATE</t>
+          <t>VARCHAR2(50)</t>
         </is>
       </c>
       <c r="C26" s="26" t="inlineStr">
         <is>
-          <t>Ngày tạo hồ sơ</t>
+          <t>Mã đơn vị kinh doanh</t>
         </is>
       </c>
       <c r="D26" s="54" t="inlineStr">
         <is>
-          <t>TRUNC(MIN(ENTRYDATE)) theo WI_NAME — nguồn NG_SB_RLOS_ENTRY_EXIT.ENTRYDATE</t>
+          <t>CỘT MỚI — BK cạnh SK: Mã đơn vị kinh doanh (BK của DIM_LOS_COMPANY layer Company)</t>
         </is>
       </c>
       <c r="E26" s="31" t="inlineStr">
         <is>
-          <t>(SELECT TRUNC(MIN(C2.ENTRYDATE)) FROM C C2 WHERE C2.WINAME = A.WI_NAME)</t>
+          <t>E.COMPANY_CODE</t>
         </is>
       </c>
     </row>
     <row r="27" ht="30" customHeight="1">
       <c r="A27" s="28" t="inlineStr">
         <is>
-          <t>APPROVED_AMT_FINAL</t>
+          <t>CHANGE_TYPE_SK</t>
         </is>
       </c>
       <c r="B27" s="25" t="inlineStr">
         <is>
-          <t>NUMBER(25,2)</t>
+          <t>NUMBER</t>
         </is>
       </c>
       <c r="C27" s="26" t="inlineStr">
         <is>
-          <t>Hạn mức phê duyệt cuối cùng</t>
+          <t>Khóa loại thay đổi</t>
         </is>
       </c>
       <c r="D27" s="54" t="inlineStr">
         <is>
-          <t>Hạn mức phê duyệt cuối cùng — nguồn NG_SB_RLOS_CREDIT_PROPOSAL.LOAN_AMOUNT</t>
+          <t>Khóa tới DIM_RLOS_CHANGE_TYPE. Chỉ có giá trị với hồ sơ thay đổi điều kiện phê duyệt, còn lại Unknown -1. Nguồn: A.CHANGE_TYPE</t>
         </is>
       </c>
       <c r="E27" s="31" t="inlineStr">
         <is>
-          <t>LEFT JOIN L ON L.WI_NAME = A.WI_NAME → L.LOAN_AMOUNT</t>
-        </is>
-      </c>
-    </row>
-    <row r="28" ht="30" customHeight="1">
+          <t>I.DIMENSION_KEY</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="60" customHeight="1">
       <c r="A28" s="28" t="inlineStr">
         <is>
-          <t>APPROVED_TERM</t>
+          <t>CHANGE_TYPE_CODE</t>
         </is>
       </c>
       <c r="B28" s="25" t="inlineStr">
         <is>
-          <t>NUMBER(15)</t>
+          <t>VARCHAR2(100)</t>
         </is>
       </c>
       <c r="C28" s="26" t="inlineStr">
         <is>
-          <t>Kỳ hạn phê duyệt</t>
+          <t>Mã loại thay đổi</t>
         </is>
       </c>
       <c r="D28" s="54" t="inlineStr">
         <is>
-          <t>Kỳ hạn phê duyệt — nguồn NG_SB_RLOS_CREDIT_PROPOSAL.LOAN_TERM</t>
+          <t>CỘT MỚI — BK cạnh SK: 1 phần BK composite (CHANGE_TYPE_CODE+DETAIL_CHANGE_TYPE_CODE) của DIM_RLOS_CHANGE_TYPE ứng với dòng đã khớp CHANGE_TYPE_SK</t>
         </is>
       </c>
       <c r="E28" s="31" t="inlineStr">
         <is>
-          <t>LEFT JOIN L ON L.WI_NAME = A.WI_NAME → L.LOAN_TERM</t>
-        </is>
-      </c>
-    </row>
-    <row r="29" ht="30" customHeight="1">
+          <t>H.CHANGE_TYPE_CODE</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="45" customHeight="1">
       <c r="A29" s="28" t="inlineStr">
         <is>
-          <t>CURRENCY_CODE</t>
+          <t>DETAIL_CHANGE_TYPE_CODE</t>
         </is>
       </c>
       <c r="B29" s="25" t="inlineStr">
         <is>
-          <t>VARCHAR2(10)</t>
+          <t>VARCHAR2(100)</t>
         </is>
       </c>
       <c r="C29" s="26" t="inlineStr">
         <is>
-          <t>Loại tiền</t>
+          <t>Mã chi tiết loại thay đổi</t>
         </is>
       </c>
       <c r="D29" s="54" t="inlineStr">
         <is>
-          <t>Loại tiền (BC3.CURRENCY) — nguồn NG_SB_RLOS_CREDIT_PROPOSAL.LOAN_CURRENCY</t>
+          <t>CỘT MỚI — BK cạnh SK: nửa còn lại BK composite DIM_RLOS_CHANGE_TYPE ứng với dòng đã khớp CHANGE_TYPE_SK</t>
         </is>
       </c>
       <c r="E29" s="31" t="inlineStr">
         <is>
-          <t>LEFT JOIN L ON L.WI_NAME = A.WI_NAME → L.LOAN_CURRENCY</t>
+          <t>H.DETAIL_CHANGE_TYPE_CODE</t>
         </is>
       </c>
     </row>
     <row r="30" ht="30" customHeight="1">
       <c r="A30" s="28" t="inlineStr">
         <is>
+          <t>CARD_PROMOTION_SK</t>
+        </is>
+      </c>
+      <c r="B30" s="25" t="inlineStr">
+        <is>
+          <t>NUMBER</t>
+        </is>
+      </c>
+      <c r="C30" s="26" t="inlineStr">
+        <is>
+          <t>Khóa ưu đãi phí thẻ</t>
+        </is>
+      </c>
+      <c r="D30" s="54" t="inlineStr">
+        <is>
+          <t>Khóa tới DIM_RLOS_CARD_PROMOTION. Lookup J.PROMOTION_ID; hồ sơ không phải thẻ dùng -1</t>
+        </is>
+      </c>
+      <c r="E30" s="31" t="inlineStr">
+        <is>
+          <t>K.DIMENSION_KEY</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="30" customHeight="1">
+      <c r="A31" s="28" t="inlineStr">
+        <is>
+          <t>PROMOTION_CODE</t>
+        </is>
+      </c>
+      <c r="B31" s="25" t="inlineStr">
+        <is>
+          <t>VARCHAR2(50)</t>
+        </is>
+      </c>
+      <c r="C31" s="26" t="inlineStr">
+        <is>
+          <t>Mã ưu đãi phí</t>
+        </is>
+      </c>
+      <c r="D31" s="54" t="inlineStr">
+        <is>
+          <t>CỘT MỚI — BK cạnh SK: Mã ưu đãi phí (BK của DIM_RLOS_CARD_PROMOTION)</t>
+        </is>
+      </c>
+      <c r="E31" s="31" t="inlineStr">
+        <is>
+          <t>J.PROMOTION_ID</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="105" customHeight="1">
+      <c r="A32" s="28" t="inlineStr">
+        <is>
+          <t>PROCESSED_DATE</t>
+        </is>
+      </c>
+      <c r="B32" s="25" t="inlineStr">
+        <is>
+          <t>DATE</t>
+        </is>
+      </c>
+      <c r="C32" s="26" t="inlineStr">
+        <is>
+          <t>Ngày xử lý hồ sơ</t>
+        </is>
+      </c>
+      <c r="D32" s="54" t="inlineStr">
+        <is>
+          <t>Ngày xử lý chung của hồ sơ theo 3 mức ưu tiên (phê duyệt cuối / hủy / hoàn tất gần nhất) — nguồn C. 3 mức ưu tiên (COALESCE theo thứ tự), đồng bộ công thức với FCT_CLOS_APPLICATION.PROCESSED_DATE: (1) MAX(EXITDATE) tại bước phê duyệt đã hoàn tất; (2) NVL(EXITDATE,ENTRYDATE) tại WORKSTEP='CancelRevoke'; (3) EXITDATE của sự kiện hoàn tất gần nhất (đối chiếu SRS BC1).</t>
+        </is>
+      </c>
+      <c r="E32" s="31" t="inlineStr">
+        <is>
+          <t>COALESCE((SELECT MAX(C.EXITDATE) FROM C WHERE C.WINAME = A.WI_NAME AND C.WORKSTEP IN ('CreditCommittee','CreditApproval') AND C.DECISION IN ('Send To HOSupport','Reject','Submit','Send To PostSanction','Submit To DisbursementMaker')), (SELECT NVL(C.EXITDATE, C.ENTRYDATE) FROM C WHERE C.WINAME = A.WI_NAME AND C.WORKSTEP = 'CancelRevoke'), (SELECT C.EXITDATE FROM C WHERE C.WINAME = A.WI_NAME AND C.EXITDATE IS NOT NULL ORDER BY C.ENTRYDATE DESC FETCH FIRST 1 ROW ONLY))</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="30" customHeight="1">
+      <c r="A33" s="28" t="inlineStr">
+        <is>
+          <t>CREATION_DATE</t>
+        </is>
+      </c>
+      <c r="B33" s="25" t="inlineStr">
+        <is>
+          <t>DATE</t>
+        </is>
+      </c>
+      <c r="C33" s="26" t="inlineStr">
+        <is>
+          <t>Ngày khởi tạo hồ sơ</t>
+        </is>
+      </c>
+      <c r="D33" s="54" t="inlineStr">
+        <is>
+          <t>TRUNC(MIN(ENTRYDATE)) theo WI_NAME — nguồn C.ENTRYDATE</t>
+        </is>
+      </c>
+      <c r="E33" s="31" t="inlineStr">
+        <is>
+          <t>(SELECT TRUNC(MIN(C.ENTRYDATE)) FROM C WHERE C.WINAME = A.WI_NAME)</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="15" customHeight="1">
+      <c r="A34" s="28" t="inlineStr">
+        <is>
+          <t>APPROVED_AMT_FINAL</t>
+        </is>
+      </c>
+      <c r="B34" s="25" t="inlineStr">
+        <is>
+          <t>NUMBER(25,2)</t>
+        </is>
+      </c>
+      <c r="C34" s="26" t="inlineStr">
+        <is>
+          <t>Hạn mức phê duyệt cuối</t>
+        </is>
+      </c>
+      <c r="D34" s="54" t="inlineStr">
+        <is>
+          <t>Hạn mức phê duyệt cuối cùng — nguồn L.LOAN_AMOUNT</t>
+        </is>
+      </c>
+      <c r="E34" s="31" t="inlineStr">
+        <is>
+          <t>L.LOAN_AMOUNT</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="15" customHeight="1">
+      <c r="A35" s="28" t="inlineStr">
+        <is>
+          <t>APPROVED_TERM</t>
+        </is>
+      </c>
+      <c r="B35" s="25" t="inlineStr">
+        <is>
+          <t>NUMBER(15)</t>
+        </is>
+      </c>
+      <c r="C35" s="26" t="inlineStr">
+        <is>
+          <t>Kỳ hạn phê duyệt</t>
+        </is>
+      </c>
+      <c r="D35" s="54" t="inlineStr">
+        <is>
+          <t>Kỳ hạn phê duyệt — nguồn L.LOAN_TERM</t>
+        </is>
+      </c>
+      <c r="E35" s="31" t="inlineStr">
+        <is>
+          <t>L.LOAN_TERM</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="90" customHeight="1">
+      <c r="A36" s="28" t="inlineStr">
+        <is>
+          <t>CURRENCY_CODE</t>
+        </is>
+      </c>
+      <c r="B36" s="25" t="inlineStr">
+        <is>
+          <t>VARCHAR2(10)</t>
+        </is>
+      </c>
+      <c r="C36" s="26" t="inlineStr">
+        <is>
+          <t>Loại tiền</t>
+        </is>
+      </c>
+      <c r="D36" s="54" t="inlineStr">
+        <is>
+          <t>Loại tiền (BC3.CURRENCY) — nguồn L.LOAN_CURRENCY. Đối chiếu SRS BC3: đặt cạnh APPROVED_AMT_FINAL/APPROVED_TERM (cùng bảng, cùng nguồn L) để BC3 lookup đủ cả 3 cột tại cùng 1 bảng đúng grain hồ sơ, thay vì tách CURRENCY_CODE sang FCT_RLOS_WORKSTEP_EVENT (không BC nào dùng ở đó).</t>
+        </is>
+      </c>
+      <c r="E36" s="31" t="inlineStr">
+        <is>
+          <t>L.LOAN_CURRENCY</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="45" customHeight="1">
+      <c r="A37" s="28" t="inlineStr">
+        <is>
           <t>CHANGE_REQUEST</t>
         </is>
       </c>
-      <c r="B30" s="25" t="inlineStr">
+      <c r="B37" s="25" t="inlineStr">
         <is>
           <t>VARCHAR2(200)</t>
         </is>
       </c>
-      <c r="C30" s="26" t="inlineStr">
+      <c r="C37" s="26" t="inlineStr">
         <is>
           <t>Yêu cầu điều chỉnh hồ sơ</t>
         </is>
       </c>
-      <c r="D30" s="54" t="inlineStr">
-        <is>
-          <t>Yêu cầu điều chỉnh hồ sơ — nguồn NG_SB_RLOS_EXTTABLE.REQ_TYPE</t>
-        </is>
-      </c>
-      <c r="E30" s="31" t="inlineStr">
+      <c r="D37" s="54" t="inlineStr">
+        <is>
+          <t>Yêu cầu điều chỉnh hồ sơ — nguồn A.REQ_TYPE. Chuyển từ DIM_RLOS_APPLICATION — bản chất thay đổi thường xuyên theo hồ sơ, không phù hợp cột ổn định SCD2 của DIM.</t>
+        </is>
+      </c>
+      <c r="E37" s="31" t="inlineStr">
         <is>
           <t>A.REQ_TYPE</t>
         </is>
       </c>
     </row>
-    <row r="31" ht="60" customHeight="1">
-      <c r="A31" s="28" t="inlineStr">
+    <row r="38" ht="120" customHeight="1">
+      <c r="A38" s="28" t="inlineStr">
         <is>
           <t>CHANGE_TYPE</t>
         </is>
       </c>
-      <c r="B31" s="25" t="inlineStr">
+      <c r="B38" s="25" t="inlineStr">
         <is>
           <t>VARCHAR2(500)</t>
         </is>
       </c>
-      <c r="C31" s="26" t="inlineStr">
-        <is>
-          <t>Loại thay đổi điều kiện phê duyệt</t>
-        </is>
-      </c>
-      <c r="D31" s="54" t="inlineStr">
-        <is>
-          <t>Loại thay đổi điều kiện phê duyệt, giữ nguyên giá trị thô. Dùng làm khóa either/or với PRODUCT_LINE khi tra cam kết SLA ở PDTD_DTM — khác CHANGE_TYPE_SK (trỏ DIM_RLOS_CHANGE_TYPE để lấy tên/chi tiết chuẩn hóa cho BC1)</t>
-        </is>
-      </c>
-      <c r="E31" s="31" t="inlineStr">
+      <c r="C38" s="26" t="inlineStr">
+        <is>
+          <t>Loại thay đổi điều kiện</t>
+        </is>
+      </c>
+      <c r="D38" s="54" t="inlineStr">
+        <is>
+          <t>Loại thay đổi điều kiện phê duyệt, giữ nguyên giá trị thô. Dùng làm khóa either/or với PRODUCT_LINE khi tra cam kết SLA ở PDTD_DTM — khác CHANGE_TYPE_SK (trỏ DIM_RLOS_CHANGE_TYPE để lấy tên/chi tiết chuẩn hóa cho BC1). Không chuyển DIM_RLOS_APPLICATION dù cùng nguồn EXTTABLE với 13 cột cờ/trạng thái khác — đây là cờ/trạng thái workflow thực sự biến động nhiều lần trong vòng đời hồ sơ, không phải 'bật 1 lần duy nhất' như nhóm cờ CREATE/DELETE_FLAG. Chuyển từ DIM_RLOS_APPLICATION.</t>
+        </is>
+      </c>
+      <c r="E38" s="31" t="inlineStr">
         <is>
           <t>A.CHANGE_TYPE</t>
+        </is>
+      </c>
+    </row>
+    <row r="40" ht="16" customHeight="1">
+      <c r="A40" s="10" t="n"/>
+      <c r="B40" s="10" t="n"/>
+      <c r="C40" s="10" t="n"/>
+      <c r="D40" s="55" t="inlineStr">
+        <is>
+          <t>Điều kiện join giữa các bảng</t>
+        </is>
+      </c>
+      <c r="E40" s="10" t="n"/>
+    </row>
+    <row r="41" ht="30" customHeight="1">
+      <c r="A41" s="25" t="n"/>
+      <c r="B41" s="25" t="n"/>
+      <c r="C41" s="51" t="n"/>
+      <c r="D41" s="54" t="n"/>
+      <c r="E41" s="8" t="inlineStr">
+        <is>
+          <t>LEFT JOIN B.WI_NAME = A.WI_NAME AND v_batch_date BETWEEN B.EFF_DATE AND NVL(B.EXP_DATE, v_batch_date)</t>
+        </is>
+      </c>
+    </row>
+    <row r="42" ht="45" customHeight="1">
+      <c r="A42" s="25" t="n"/>
+      <c r="B42" s="25" t="n"/>
+      <c r="C42" s="51" t="n"/>
+      <c r="D42" s="54" t="n"/>
+      <c r="E42" s="8" t="inlineStr">
+        <is>
+          <t>LEFT JOIN (SELECT C.WORKSTEP, C.DECISION FROM C WHERE C.WINAME = A.WI_NAME AND C.EXITDATE IS NOT NULL AND C.ENTRYDATE &lt;= v_batch_date ORDER BY C.ENTRYDATE DESC FETCH FIRST 1 ROW ONLY) LAST_EVENT ON 1=1</t>
+        </is>
+      </c>
+    </row>
+    <row r="43" ht="45" customHeight="1">
+      <c r="A43" s="25" t="n"/>
+      <c r="B43" s="25" t="n"/>
+      <c r="C43" s="51" t="n"/>
+      <c r="D43" s="54" t="n"/>
+      <c r="E43" s="8" t="inlineStr">
+        <is>
+          <t>LEFT JOIN D.WORKSTEP_CODE = LAST_EVENT.WORKSTEP AND D.DECISION_CODE = LAST_EVENT.DECISION AND v_batch_date BETWEEN D.EFF_DATE AND NVL(D.EXP_DATE, v_batch_date)</t>
+        </is>
+      </c>
+    </row>
+    <row r="44" ht="15" customHeight="1">
+      <c r="A44" s="25" t="n"/>
+      <c r="B44" s="25" t="n"/>
+      <c r="C44" s="51" t="n"/>
+      <c r="D44" s="54" t="n"/>
+      <c r="E44" s="8" t="inlineStr">
+        <is>
+          <t>LEFT JOIN E.WI_NAME = A.WI_NAME</t>
+        </is>
+      </c>
+    </row>
+    <row r="45" ht="45" customHeight="1">
+      <c r="A45" s="25" t="n"/>
+      <c r="B45" s="25" t="n"/>
+      <c r="C45" s="51" t="n"/>
+      <c r="D45" s="54" t="n"/>
+      <c r="E45" s="8" t="inlineStr">
+        <is>
+          <t>LEFT JOIN F.PRODUCTLINE_CODE = E.PRODUCT_LINE AND F.SUB_PRODUCT_NAME = E.SUB_PRODUCT AND v_batch_date BETWEEN F.EFF_DATE AND NVL(F.EXP_DATE, v_batch_date)</t>
+        </is>
+      </c>
+    </row>
+    <row r="46" ht="30" customHeight="1">
+      <c r="A46" s="25" t="n"/>
+      <c r="B46" s="25" t="n"/>
+      <c r="C46" s="51" t="n"/>
+      <c r="D46" s="54" t="n"/>
+      <c r="E46" s="8" t="inlineStr">
+        <is>
+          <t>LEFT JOIN G.COMPANY_CODE = E.COMPANY_CODE AND v_batch_date BETWEEN G.COMPANY_EFF_DATE AND NVL(G.COMPANY_EXP_DATE, v_batch_date)</t>
+        </is>
+      </c>
+    </row>
+    <row r="47" ht="15" customHeight="1">
+      <c r="A47" s="25" t="n"/>
+      <c r="B47" s="25" t="n"/>
+      <c r="C47" s="51" t="n"/>
+      <c r="D47" s="54" t="n"/>
+      <c r="E47" s="8" t="inlineStr">
+        <is>
+          <t>LEFT JOIN H.WI_NAME = A.WI_NAME</t>
+        </is>
+      </c>
+    </row>
+    <row r="48" ht="30" customHeight="1">
+      <c r="A48" s="25" t="n"/>
+      <c r="B48" s="25" t="n"/>
+      <c r="C48" s="51" t="n"/>
+      <c r="D48" s="54" t="n"/>
+      <c r="E48" s="8" t="inlineStr">
+        <is>
+          <t>LEFT JOIN I.CHANGE_TYPE_CODE = H.CHANGE_TYPE_CODE AND I.DETAIL_CHANGE_TYPE_CODE = H.DETAIL_CHANGE_TYPE_CODE</t>
+        </is>
+      </c>
+    </row>
+    <row r="49" ht="15" customHeight="1">
+      <c r="A49" s="25" t="n"/>
+      <c r="B49" s="25" t="n"/>
+      <c r="C49" s="51" t="n"/>
+      <c r="D49" s="54" t="n"/>
+      <c r="E49" s="8" t="inlineStr">
+        <is>
+          <t>LEFT JOIN J.WI_NAME = A.WI_NAME</t>
+        </is>
+      </c>
+    </row>
+    <row r="50" ht="15" customHeight="1">
+      <c r="A50" s="25" t="n"/>
+      <c r="B50" s="25" t="n"/>
+      <c r="C50" s="51" t="n"/>
+      <c r="D50" s="54" t="n"/>
+      <c r="E50" s="8" t="inlineStr">
+        <is>
+          <t>LEFT JOIN K.PROMOTION_CODE = J.PROMOTION_ID</t>
+        </is>
+      </c>
+    </row>
+    <row r="51" ht="15" customHeight="1">
+      <c r="A51" s="25" t="n"/>
+      <c r="B51" s="25" t="n"/>
+      <c r="C51" s="51" t="n"/>
+      <c r="D51" s="54" t="n"/>
+      <c r="E51" s="8" t="inlineStr">
+        <is>
+          <t>LEFT JOIN L.WI_NAME = A.WI_NAME</t>
         </is>
       </c>
     </row>

--- a/mapping/SB_DWH/Mapping_FCT_RLOS_APPLICATION.xlsx
+++ b/mapping/SB_DWH/Mapping_FCT_RLOS_APPLICATION.xlsx
@@ -718,7 +718,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E51"/>
+  <dimension ref="A1:E52"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.1640625" defaultRowHeight="16"/>
   <cols>
     <col width="34.33203125" customWidth="1" style="19" min="1" max="1"/>
@@ -989,7 +989,7 @@
         </is>
       </c>
     </row>
-    <row r="20" ht="120" customHeight="1">
+    <row r="20" ht="75" customHeight="1">
       <c r="A20" s="28" t="inlineStr">
         <is>
           <t>WORKSTEP_DECISION_SK</t>
@@ -1007,7 +1007,7 @@
       </c>
       <c r="D20" s="54" t="inlineStr">
         <is>
-          <t>Khóa tới DIM_RLOS_WORKSTEP_DECISION (gộp từ LAST_WORKSTEP_SK+LAST_DECISION_SK) của sự kiện hoàn tất gần nhất, lookup theo cặp WORKSTEP_CODE+DECISION_CODE của sự kiện đó. Mặc định -1 — đổi tên từ LAST_WORKSTEP_DECISION_SK. Lookup theo cặp WORKSTEP_CODE+DECISION_CODE của sự kiện hoàn tất gần nhất (LAST_EVENT = dòng có ENTRYDATE lớn nhất, EXITDATE IS NOT NULL, tính đến v_batch_date).</t>
+          <t>Khóa tới DIM_RLOS_WORKSTEP_DECISION (gộp từ LAST_WORKSTEP_SK+LAST_DECISION_SK) của sự kiện hoàn tất gần nhất, lookup theo cặp WORKSTEP_CODE+DECISION_CODE của sự kiện đó. Mặc định -1 — đổi tên từ LAST_WORKSTEP_DECISION_SK</t>
         </is>
       </c>
       <c r="E20" s="31" t="inlineStr">
@@ -1097,441 +1097,457 @@
         </is>
       </c>
     </row>
-    <row r="24" ht="45" customHeight="1">
+    <row r="24" ht="60" customHeight="1">
       <c r="A24" s="28" t="inlineStr">
         <is>
+          <t>PRODUCTLINE_CODE</t>
+        </is>
+      </c>
+      <c r="B24" s="25" t="inlineStr">
+        <is>
+          <t>VARCHAR2(100)</t>
+        </is>
+      </c>
+      <c r="C24" s="26" t="inlineStr">
+        <is>
+          <t>Mã dòng sản phẩm</t>
+        </is>
+      </c>
+      <c r="D24" s="54" t="inlineStr">
+        <is>
+          <t>CỘT MỚI (review 2026-10-27) — BK cạnh SK: nửa còn lại của cặp khóa lookup DIM_RLOS_PRODUCT (cùng SUB_PRODUCT_NAME) cần để tra SUB_PRODUCT_SK — nguồn E.PRODUCT_LINE, cùng giá trị đã dùng để lookup SUB_PRODUCT_SK, không JOIN thêm.</t>
+        </is>
+      </c>
+      <c r="E24" s="31" t="inlineStr">
+        <is>
+          <t>E.PRODUCT_LINE</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="45" customHeight="1">
+      <c r="A25" s="28" t="inlineStr">
+        <is>
           <t>SUB_PRODUCT_CODE</t>
         </is>
       </c>
-      <c r="B24" s="25" t="inlineStr">
+      <c r="B25" s="25" t="inlineStr">
         <is>
           <t>VARCHAR2(100)</t>
         </is>
       </c>
-      <c r="C24" s="26" t="inlineStr">
+      <c r="C25" s="26" t="inlineStr">
         <is>
           <t>Mã sản phẩm nhánh</t>
         </is>
       </c>
-      <c r="D24" s="54" t="inlineStr">
+      <c r="D25" s="54" t="inlineStr">
         <is>
           <t>CỘT MỚI — BK cạnh SK: Mã sản phẩm nhánh (BK thật của DIM_RLOS_PRODUCT layer Sub Product — khác SUB_PRODUCT_NAME dùng làm điều kiện JOIN)</t>
         </is>
       </c>
-      <c r="E24" s="31" t="inlineStr">
+      <c r="E25" s="31" t="inlineStr">
         <is>
           <t>F.SUB_PRODUCT_CODE</t>
         </is>
       </c>
     </row>
-    <row r="25" ht="135" customHeight="1">
-      <c r="A25" s="28" t="inlineStr">
+    <row r="26" ht="75" customHeight="1">
+      <c r="A26" s="28" t="inlineStr">
         <is>
           <t>COMPANY_SK</t>
         </is>
       </c>
-      <c r="B25" s="25" t="inlineStr">
+      <c r="B26" s="25" t="inlineStr">
         <is>
           <t>NUMBER</t>
         </is>
       </c>
-      <c r="C25" s="26" t="inlineStr">
+      <c r="C26" s="26" t="inlineStr">
         <is>
           <t>Khóa đơn vị kinh doanh</t>
         </is>
       </c>
-      <c r="D25" s="54" t="inlineStr">
-        <is>
-          <t>Khóa tới DIM_LOS_COMPANY — PHÁI SINH: lookup theo COMPANY_CODE=E.COMPANY_CODE, điều kiện SCD2 COMPANY_EFF_DATE&lt;=DAYID&lt;COMPANY_EXP_DATE (hoặc COMPANY_EXP_DATE IS NULL) theo layer Company trên DIM_LOS_COMPANY. Mặc định -1 nếu không khớp. Thay thế ORG_UNIT_SK cũ. Lookup theo layer Company (COMPANY_EFF_DATE/COMPANY_EXP_DATE), thay cho EFF_DATE/EXP_DATE chung cũ — DIM_LOS_COMPANY tách 3 layer SCD2 độc lập.</t>
-        </is>
-      </c>
-      <c r="E25" s="31" t="inlineStr">
+      <c r="D26" s="54" t="inlineStr">
+        <is>
+          <t>Khóa tới DIM_LOS_COMPANY — PHÁI SINH: lookup theo COMPANY_CODE=E.COMPANY_CODE, điều kiện SCD2 COMPANY_EFF_DATE&lt;=DAYID&lt;COMPANY_EXP_DATE (hoặc COMPANY_EXP_DATE IS NULL) theo layer Company trên DIM_LOS_COMPANY. Mặc định -1 nếu không khớp</t>
+        </is>
+      </c>
+      <c r="E26" s="31" t="inlineStr">
         <is>
           <t>G.DIMENSION_KEY</t>
-        </is>
-      </c>
-    </row>
-    <row r="26" ht="30" customHeight="1">
-      <c r="A26" s="28" t="inlineStr">
-        <is>
-          <t>COMPANY_CODE</t>
-        </is>
-      </c>
-      <c r="B26" s="25" t="inlineStr">
-        <is>
-          <t>VARCHAR2(50)</t>
-        </is>
-      </c>
-      <c r="C26" s="26" t="inlineStr">
-        <is>
-          <t>Mã đơn vị kinh doanh</t>
-        </is>
-      </c>
-      <c r="D26" s="54" t="inlineStr">
-        <is>
-          <t>CỘT MỚI — BK cạnh SK: Mã đơn vị kinh doanh (BK của DIM_LOS_COMPANY layer Company)</t>
-        </is>
-      </c>
-      <c r="E26" s="31" t="inlineStr">
-        <is>
-          <t>E.COMPANY_CODE</t>
         </is>
       </c>
     </row>
     <row r="27" ht="30" customHeight="1">
       <c r="A27" s="28" t="inlineStr">
         <is>
+          <t>COMPANY_CODE</t>
+        </is>
+      </c>
+      <c r="B27" s="25" t="inlineStr">
+        <is>
+          <t>VARCHAR2(50)</t>
+        </is>
+      </c>
+      <c r="C27" s="26" t="inlineStr">
+        <is>
+          <t>Mã đơn vị kinh doanh</t>
+        </is>
+      </c>
+      <c r="D27" s="54" t="inlineStr">
+        <is>
+          <t>CỘT MỚI — BK cạnh SK: Mã đơn vị kinh doanh (BK của DIM_LOS_COMPANY layer Company)</t>
+        </is>
+      </c>
+      <c r="E27" s="31" t="inlineStr">
+        <is>
+          <t>E.COMPANY_CODE</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="30" customHeight="1">
+      <c r="A28" s="28" t="inlineStr">
+        <is>
           <t>CHANGE_TYPE_SK</t>
         </is>
       </c>
-      <c r="B27" s="25" t="inlineStr">
+      <c r="B28" s="25" t="inlineStr">
         <is>
           <t>NUMBER</t>
         </is>
       </c>
-      <c r="C27" s="26" t="inlineStr">
+      <c r="C28" s="26" t="inlineStr">
         <is>
           <t>Khóa loại thay đổi</t>
         </is>
       </c>
-      <c r="D27" s="54" t="inlineStr">
+      <c r="D28" s="54" t="inlineStr">
         <is>
           <t>Khóa tới DIM_RLOS_CHANGE_TYPE. Chỉ có giá trị với hồ sơ thay đổi điều kiện phê duyệt, còn lại Unknown -1. Nguồn: A.CHANGE_TYPE</t>
         </is>
       </c>
-      <c r="E27" s="31" t="inlineStr">
+      <c r="E28" s="31" t="inlineStr">
         <is>
           <t>I.DIMENSION_KEY</t>
         </is>
       </c>
     </row>
-    <row r="28" ht="60" customHeight="1">
-      <c r="A28" s="28" t="inlineStr">
+    <row r="29" ht="60" customHeight="1">
+      <c r="A29" s="28" t="inlineStr">
         <is>
           <t>CHANGE_TYPE_CODE</t>
         </is>
       </c>
-      <c r="B28" s="25" t="inlineStr">
+      <c r="B29" s="25" t="inlineStr">
         <is>
           <t>VARCHAR2(100)</t>
         </is>
       </c>
-      <c r="C28" s="26" t="inlineStr">
+      <c r="C29" s="26" t="inlineStr">
         <is>
           <t>Mã loại thay đổi</t>
         </is>
       </c>
-      <c r="D28" s="54" t="inlineStr">
+      <c r="D29" s="54" t="inlineStr">
         <is>
           <t>CỘT MỚI — BK cạnh SK: 1 phần BK composite (CHANGE_TYPE_CODE+DETAIL_CHANGE_TYPE_CODE) của DIM_RLOS_CHANGE_TYPE ứng với dòng đã khớp CHANGE_TYPE_SK</t>
         </is>
       </c>
-      <c r="E28" s="31" t="inlineStr">
+      <c r="E29" s="31" t="inlineStr">
         <is>
           <t>H.CHANGE_TYPE_CODE</t>
         </is>
       </c>
     </row>
-    <row r="29" ht="45" customHeight="1">
-      <c r="A29" s="28" t="inlineStr">
+    <row r="30" ht="45" customHeight="1">
+      <c r="A30" s="28" t="inlineStr">
         <is>
           <t>DETAIL_CHANGE_TYPE_CODE</t>
         </is>
       </c>
-      <c r="B29" s="25" t="inlineStr">
+      <c r="B30" s="25" t="inlineStr">
         <is>
           <t>VARCHAR2(100)</t>
         </is>
       </c>
-      <c r="C29" s="26" t="inlineStr">
+      <c r="C30" s="26" t="inlineStr">
         <is>
           <t>Mã chi tiết loại thay đổi</t>
         </is>
       </c>
-      <c r="D29" s="54" t="inlineStr">
+      <c r="D30" s="54" t="inlineStr">
         <is>
           <t>CỘT MỚI — BK cạnh SK: nửa còn lại BK composite DIM_RLOS_CHANGE_TYPE ứng với dòng đã khớp CHANGE_TYPE_SK</t>
         </is>
       </c>
-      <c r="E29" s="31" t="inlineStr">
+      <c r="E30" s="31" t="inlineStr">
         <is>
           <t>H.DETAIL_CHANGE_TYPE_CODE</t>
-        </is>
-      </c>
-    </row>
-    <row r="30" ht="30" customHeight="1">
-      <c r="A30" s="28" t="inlineStr">
-        <is>
-          <t>CARD_PROMOTION_SK</t>
-        </is>
-      </c>
-      <c r="B30" s="25" t="inlineStr">
-        <is>
-          <t>NUMBER</t>
-        </is>
-      </c>
-      <c r="C30" s="26" t="inlineStr">
-        <is>
-          <t>Khóa ưu đãi phí thẻ</t>
-        </is>
-      </c>
-      <c r="D30" s="54" t="inlineStr">
-        <is>
-          <t>Khóa tới DIM_RLOS_CARD_PROMOTION. Lookup J.PROMOTION_ID; hồ sơ không phải thẻ dùng -1</t>
-        </is>
-      </c>
-      <c r="E30" s="31" t="inlineStr">
-        <is>
-          <t>K.DIMENSION_KEY</t>
         </is>
       </c>
     </row>
     <row r="31" ht="30" customHeight="1">
       <c r="A31" s="28" t="inlineStr">
         <is>
+          <t>CARD_PROMOTION_SK</t>
+        </is>
+      </c>
+      <c r="B31" s="25" t="inlineStr">
+        <is>
+          <t>NUMBER</t>
+        </is>
+      </c>
+      <c r="C31" s="26" t="inlineStr">
+        <is>
+          <t>Khóa ưu đãi phí thẻ</t>
+        </is>
+      </c>
+      <c r="D31" s="54" t="inlineStr">
+        <is>
+          <t>Khóa tới DIM_RLOS_CARD_PROMOTION. Lookup J.PROMOTION_ID; hồ sơ không phải thẻ dùng -1</t>
+        </is>
+      </c>
+      <c r="E31" s="31" t="inlineStr">
+        <is>
+          <t>K.DIMENSION_KEY</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="30" customHeight="1">
+      <c r="A32" s="28" t="inlineStr">
+        <is>
           <t>PROMOTION_CODE</t>
         </is>
       </c>
-      <c r="B31" s="25" t="inlineStr">
+      <c r="B32" s="25" t="inlineStr">
         <is>
           <t>VARCHAR2(50)</t>
         </is>
       </c>
-      <c r="C31" s="26" t="inlineStr">
+      <c r="C32" s="26" t="inlineStr">
         <is>
           <t>Mã ưu đãi phí</t>
         </is>
       </c>
-      <c r="D31" s="54" t="inlineStr">
+      <c r="D32" s="54" t="inlineStr">
         <is>
           <t>CỘT MỚI — BK cạnh SK: Mã ưu đãi phí (BK của DIM_RLOS_CARD_PROMOTION)</t>
         </is>
       </c>
-      <c r="E31" s="31" t="inlineStr">
+      <c r="E32" s="31" t="inlineStr">
         <is>
           <t>J.PROMOTION_ID</t>
         </is>
       </c>
     </row>
-    <row r="32" ht="105" customHeight="1">
-      <c r="A32" s="28" t="inlineStr">
+    <row r="33" ht="105" customHeight="1">
+      <c r="A33" s="28" t="inlineStr">
         <is>
           <t>PROCESSED_DATE</t>
         </is>
       </c>
-      <c r="B32" s="25" t="inlineStr">
+      <c r="B33" s="25" t="inlineStr">
         <is>
           <t>DATE</t>
         </is>
       </c>
-      <c r="C32" s="26" t="inlineStr">
+      <c r="C33" s="26" t="inlineStr">
         <is>
           <t>Ngày xử lý hồ sơ</t>
         </is>
       </c>
-      <c r="D32" s="54" t="inlineStr">
+      <c r="D33" s="54" t="inlineStr">
         <is>
           <t>Ngày xử lý chung của hồ sơ theo 3 mức ưu tiên (phê duyệt cuối / hủy / hoàn tất gần nhất) — nguồn C. 3 mức ưu tiên (COALESCE theo thứ tự), đồng bộ công thức với FCT_CLOS_APPLICATION.PROCESSED_DATE: (1) MAX(EXITDATE) tại bước phê duyệt đã hoàn tất; (2) NVL(EXITDATE,ENTRYDATE) tại WORKSTEP='CancelRevoke'; (3) EXITDATE của sự kiện hoàn tất gần nhất (đối chiếu SRS BC1).</t>
         </is>
       </c>
-      <c r="E32" s="31" t="inlineStr">
+      <c r="E33" s="31" t="inlineStr">
         <is>
           <t>COALESCE((SELECT MAX(C.EXITDATE) FROM C WHERE C.WINAME = A.WI_NAME AND C.WORKSTEP IN ('CreditCommittee','CreditApproval') AND C.DECISION IN ('Send To HOSupport','Reject','Submit','Send To PostSanction','Submit To DisbursementMaker')), (SELECT NVL(C.EXITDATE, C.ENTRYDATE) FROM C WHERE C.WINAME = A.WI_NAME AND C.WORKSTEP = 'CancelRevoke'), (SELECT C.EXITDATE FROM C WHERE C.WINAME = A.WI_NAME AND C.EXITDATE IS NOT NULL ORDER BY C.ENTRYDATE DESC FETCH FIRST 1 ROW ONLY))</t>
         </is>
       </c>
     </row>
-    <row r="33" ht="30" customHeight="1">
-      <c r="A33" s="28" t="inlineStr">
+    <row r="34" ht="30" customHeight="1">
+      <c r="A34" s="28" t="inlineStr">
         <is>
           <t>CREATION_DATE</t>
         </is>
       </c>
-      <c r="B33" s="25" t="inlineStr">
+      <c r="B34" s="25" t="inlineStr">
         <is>
           <t>DATE</t>
         </is>
       </c>
-      <c r="C33" s="26" t="inlineStr">
+      <c r="C34" s="26" t="inlineStr">
         <is>
           <t>Ngày khởi tạo hồ sơ</t>
         </is>
       </c>
-      <c r="D33" s="54" t="inlineStr">
+      <c r="D34" s="54" t="inlineStr">
         <is>
           <t>TRUNC(MIN(ENTRYDATE)) theo WI_NAME — nguồn C.ENTRYDATE</t>
         </is>
       </c>
-      <c r="E33" s="31" t="inlineStr">
+      <c r="E34" s="31" t="inlineStr">
         <is>
           <t>(SELECT TRUNC(MIN(C.ENTRYDATE)) FROM C WHERE C.WINAME = A.WI_NAME)</t>
-        </is>
-      </c>
-    </row>
-    <row r="34" ht="15" customHeight="1">
-      <c r="A34" s="28" t="inlineStr">
-        <is>
-          <t>APPROVED_AMT_FINAL</t>
-        </is>
-      </c>
-      <c r="B34" s="25" t="inlineStr">
-        <is>
-          <t>NUMBER(25,2)</t>
-        </is>
-      </c>
-      <c r="C34" s="26" t="inlineStr">
-        <is>
-          <t>Hạn mức phê duyệt cuối</t>
-        </is>
-      </c>
-      <c r="D34" s="54" t="inlineStr">
-        <is>
-          <t>Hạn mức phê duyệt cuối cùng — nguồn L.LOAN_AMOUNT</t>
-        </is>
-      </c>
-      <c r="E34" s="31" t="inlineStr">
-        <is>
-          <t>L.LOAN_AMOUNT</t>
         </is>
       </c>
     </row>
     <row r="35" ht="15" customHeight="1">
       <c r="A35" s="28" t="inlineStr">
         <is>
+          <t>APPROVED_AMT_FINAL</t>
+        </is>
+      </c>
+      <c r="B35" s="25" t="inlineStr">
+        <is>
+          <t>NUMBER(25,2)</t>
+        </is>
+      </c>
+      <c r="C35" s="26" t="inlineStr">
+        <is>
+          <t>Hạn mức phê duyệt cuối</t>
+        </is>
+      </c>
+      <c r="D35" s="54" t="inlineStr">
+        <is>
+          <t>Hạn mức phê duyệt cuối cùng — nguồn L.LOAN_AMOUNT</t>
+        </is>
+      </c>
+      <c r="E35" s="31" t="inlineStr">
+        <is>
+          <t>L.LOAN_AMOUNT</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="15" customHeight="1">
+      <c r="A36" s="28" t="inlineStr">
+        <is>
           <t>APPROVED_TERM</t>
         </is>
       </c>
-      <c r="B35" s="25" t="inlineStr">
+      <c r="B36" s="25" t="inlineStr">
         <is>
           <t>NUMBER(15)</t>
         </is>
       </c>
-      <c r="C35" s="26" t="inlineStr">
+      <c r="C36" s="26" t="inlineStr">
         <is>
           <t>Kỳ hạn phê duyệt</t>
         </is>
       </c>
-      <c r="D35" s="54" t="inlineStr">
+      <c r="D36" s="54" t="inlineStr">
         <is>
           <t>Kỳ hạn phê duyệt — nguồn L.LOAN_TERM</t>
         </is>
       </c>
-      <c r="E35" s="31" t="inlineStr">
+      <c r="E36" s="31" t="inlineStr">
         <is>
           <t>L.LOAN_TERM</t>
         </is>
       </c>
     </row>
-    <row r="36" ht="90" customHeight="1">
-      <c r="A36" s="28" t="inlineStr">
+    <row r="37" ht="90" customHeight="1">
+      <c r="A37" s="28" t="inlineStr">
         <is>
           <t>CURRENCY_CODE</t>
         </is>
       </c>
-      <c r="B36" s="25" t="inlineStr">
+      <c r="B37" s="25" t="inlineStr">
         <is>
           <t>VARCHAR2(10)</t>
         </is>
       </c>
-      <c r="C36" s="26" t="inlineStr">
+      <c r="C37" s="26" t="inlineStr">
         <is>
           <t>Loại tiền</t>
         </is>
       </c>
-      <c r="D36" s="54" t="inlineStr">
+      <c r="D37" s="54" t="inlineStr">
         <is>
           <t>Loại tiền (BC3.CURRENCY) — nguồn L.LOAN_CURRENCY. Đối chiếu SRS BC3: đặt cạnh APPROVED_AMT_FINAL/APPROVED_TERM (cùng bảng, cùng nguồn L) để BC3 lookup đủ cả 3 cột tại cùng 1 bảng đúng grain hồ sơ, thay vì tách CURRENCY_CODE sang FCT_RLOS_WORKSTEP_EVENT (không BC nào dùng ở đó).</t>
         </is>
       </c>
-      <c r="E36" s="31" t="inlineStr">
+      <c r="E37" s="31" t="inlineStr">
         <is>
           <t>L.LOAN_CURRENCY</t>
         </is>
       </c>
     </row>
-    <row r="37" ht="45" customHeight="1">
-      <c r="A37" s="28" t="inlineStr">
+    <row r="38" ht="45" customHeight="1">
+      <c r="A38" s="28" t="inlineStr">
         <is>
           <t>CHANGE_REQUEST</t>
         </is>
       </c>
-      <c r="B37" s="25" t="inlineStr">
+      <c r="B38" s="25" t="inlineStr">
         <is>
           <t>VARCHAR2(200)</t>
         </is>
       </c>
-      <c r="C37" s="26" t="inlineStr">
+      <c r="C38" s="26" t="inlineStr">
         <is>
           <t>Yêu cầu điều chỉnh hồ sơ</t>
         </is>
       </c>
-      <c r="D37" s="54" t="inlineStr">
+      <c r="D38" s="54" t="inlineStr">
         <is>
           <t>Yêu cầu điều chỉnh hồ sơ — nguồn A.REQ_TYPE. Chuyển từ DIM_RLOS_APPLICATION — bản chất thay đổi thường xuyên theo hồ sơ, không phù hợp cột ổn định SCD2 của DIM.</t>
         </is>
       </c>
-      <c r="E37" s="31" t="inlineStr">
+      <c r="E38" s="31" t="inlineStr">
         <is>
           <t>A.REQ_TYPE</t>
         </is>
       </c>
     </row>
-    <row r="38" ht="120" customHeight="1">
-      <c r="A38" s="28" t="inlineStr">
+    <row r="39" ht="120" customHeight="1">
+      <c r="A39" s="28" t="inlineStr">
         <is>
           <t>CHANGE_TYPE</t>
         </is>
       </c>
-      <c r="B38" s="25" t="inlineStr">
+      <c r="B39" s="25" t="inlineStr">
         <is>
           <t>VARCHAR2(500)</t>
         </is>
       </c>
-      <c r="C38" s="26" t="inlineStr">
+      <c r="C39" s="26" t="inlineStr">
         <is>
           <t>Loại thay đổi điều kiện</t>
         </is>
       </c>
-      <c r="D38" s="54" t="inlineStr">
+      <c r="D39" s="54" t="inlineStr">
         <is>
           <t>Loại thay đổi điều kiện phê duyệt, giữ nguyên giá trị thô. Dùng làm khóa either/or với PRODUCT_LINE khi tra cam kết SLA ở PDTD_DTM — khác CHANGE_TYPE_SK (trỏ DIM_RLOS_CHANGE_TYPE để lấy tên/chi tiết chuẩn hóa cho BC1). Không chuyển DIM_RLOS_APPLICATION dù cùng nguồn EXTTABLE với 13 cột cờ/trạng thái khác — đây là cờ/trạng thái workflow thực sự biến động nhiều lần trong vòng đời hồ sơ, không phải 'bật 1 lần duy nhất' như nhóm cờ CREATE/DELETE_FLAG. Chuyển từ DIM_RLOS_APPLICATION.</t>
         </is>
       </c>
-      <c r="E38" s="31" t="inlineStr">
+      <c r="E39" s="31" t="inlineStr">
         <is>
           <t>A.CHANGE_TYPE</t>
         </is>
       </c>
     </row>
-    <row r="40" ht="16" customHeight="1">
-      <c r="A40" s="10" t="n"/>
-      <c r="B40" s="10" t="n"/>
-      <c r="C40" s="10" t="n"/>
-      <c r="D40" s="55" t="inlineStr">
+    <row r="41" ht="16" customHeight="1">
+      <c r="A41" s="10" t="n"/>
+      <c r="B41" s="10" t="n"/>
+      <c r="C41" s="10" t="n"/>
+      <c r="D41" s="55" t="inlineStr">
         <is>
           <t>Điều kiện join giữa các bảng</t>
         </is>
       </c>
-      <c r="E40" s="10" t="n"/>
-    </row>
-    <row r="41" ht="30" customHeight="1">
-      <c r="A41" s="25" t="n"/>
-      <c r="B41" s="25" t="n"/>
-      <c r="C41" s="51" t="n"/>
-      <c r="D41" s="54" t="n"/>
-      <c r="E41" s="8" t="inlineStr">
-        <is>
-          <t>LEFT JOIN B.WI_NAME = A.WI_NAME AND v_batch_date BETWEEN B.EFF_DATE AND NVL(B.EXP_DATE, v_batch_date)</t>
-        </is>
-      </c>
-    </row>
-    <row r="42" ht="45" customHeight="1">
+      <c r="E41" s="10" t="n"/>
+    </row>
+    <row r="42" ht="30" customHeight="1">
       <c r="A42" s="25" t="n"/>
       <c r="B42" s="25" t="n"/>
       <c r="C42" s="51" t="n"/>
       <c r="D42" s="54" t="n"/>
       <c r="E42" s="8" t="inlineStr">
         <is>
-          <t>LEFT JOIN (SELECT C.WORKSTEP, C.DECISION FROM C WHERE C.WINAME = A.WI_NAME AND C.EXITDATE IS NOT NULL AND C.ENTRYDATE &lt;= v_batch_date ORDER BY C.ENTRYDATE DESC FETCH FIRST 1 ROW ONLY) LAST_EVENT ON 1=1</t>
+          <t>LEFT JOIN B.WI_NAME = A.WI_NAME AND v_batch_date BETWEEN B.EFF_DATE AND NVL(B.EXP_DATE, v_batch_date)</t>
         </is>
       </c>
     </row>
@@ -1542,73 +1558,73 @@
       <c r="D43" s="54" t="n"/>
       <c r="E43" s="8" t="inlineStr">
         <is>
-          <t>LEFT JOIN D.WORKSTEP_CODE = LAST_EVENT.WORKSTEP AND D.DECISION_CODE = LAST_EVENT.DECISION AND v_batch_date BETWEEN D.EFF_DATE AND NVL(D.EXP_DATE, v_batch_date)</t>
-        </is>
-      </c>
-    </row>
-    <row r="44" ht="15" customHeight="1">
+          <t>LEFT JOIN (SELECT C.WORKSTEP, C.DECISION FROM C WHERE C.WINAME = A.WI_NAME AND C.EXITDATE IS NOT NULL AND C.ENTRYDATE &lt;= v_batch_date ORDER BY C.ENTRYDATE DESC FETCH FIRST 1 ROW ONLY) LAST_EVENT ON 1=1</t>
+        </is>
+      </c>
+    </row>
+    <row r="44" ht="45" customHeight="1">
       <c r="A44" s="25" t="n"/>
       <c r="B44" s="25" t="n"/>
       <c r="C44" s="51" t="n"/>
       <c r="D44" s="54" t="n"/>
       <c r="E44" s="8" t="inlineStr">
         <is>
-          <t>LEFT JOIN E.WI_NAME = A.WI_NAME</t>
-        </is>
-      </c>
-    </row>
-    <row r="45" ht="45" customHeight="1">
+          <t>LEFT JOIN D.WORKSTEP_CODE = LAST_EVENT.WORKSTEP AND D.DECISION_CODE = LAST_EVENT.DECISION AND v_batch_date BETWEEN D.EFF_DATE AND NVL(D.EXP_DATE, v_batch_date)</t>
+        </is>
+      </c>
+    </row>
+    <row r="45" ht="15" customHeight="1">
       <c r="A45" s="25" t="n"/>
       <c r="B45" s="25" t="n"/>
       <c r="C45" s="51" t="n"/>
       <c r="D45" s="54" t="n"/>
       <c r="E45" s="8" t="inlineStr">
         <is>
-          <t>LEFT JOIN F.PRODUCTLINE_CODE = E.PRODUCT_LINE AND F.SUB_PRODUCT_NAME = E.SUB_PRODUCT AND v_batch_date BETWEEN F.EFF_DATE AND NVL(F.EXP_DATE, v_batch_date)</t>
-        </is>
-      </c>
-    </row>
-    <row r="46" ht="30" customHeight="1">
+          <t>LEFT JOIN E.WI_NAME = A.WI_NAME</t>
+        </is>
+      </c>
+    </row>
+    <row r="46" ht="45" customHeight="1">
       <c r="A46" s="25" t="n"/>
       <c r="B46" s="25" t="n"/>
       <c r="C46" s="51" t="n"/>
       <c r="D46" s="54" t="n"/>
       <c r="E46" s="8" t="inlineStr">
         <is>
-          <t>LEFT JOIN G.COMPANY_CODE = E.COMPANY_CODE AND v_batch_date BETWEEN G.COMPANY_EFF_DATE AND NVL(G.COMPANY_EXP_DATE, v_batch_date)</t>
-        </is>
-      </c>
-    </row>
-    <row r="47" ht="15" customHeight="1">
+          <t>LEFT JOIN F.PRODUCTLINE_CODE = E.PRODUCT_LINE AND F.SUB_PRODUCT_NAME = E.SUB_PRODUCT AND v_batch_date BETWEEN F.EFF_DATE AND NVL(F.EXP_DATE, v_batch_date)</t>
+        </is>
+      </c>
+    </row>
+    <row r="47" ht="30" customHeight="1">
       <c r="A47" s="25" t="n"/>
       <c r="B47" s="25" t="n"/>
       <c r="C47" s="51" t="n"/>
       <c r="D47" s="54" t="n"/>
       <c r="E47" s="8" t="inlineStr">
         <is>
-          <t>LEFT JOIN H.WI_NAME = A.WI_NAME</t>
-        </is>
-      </c>
-    </row>
-    <row r="48" ht="30" customHeight="1">
+          <t>LEFT JOIN G.COMPANY_CODE = E.COMPANY_CODE AND v_batch_date BETWEEN G.COMPANY_EFF_DATE AND NVL(G.COMPANY_EXP_DATE, v_batch_date)</t>
+        </is>
+      </c>
+    </row>
+    <row r="48" ht="15" customHeight="1">
       <c r="A48" s="25" t="n"/>
       <c r="B48" s="25" t="n"/>
       <c r="C48" s="51" t="n"/>
       <c r="D48" s="54" t="n"/>
       <c r="E48" s="8" t="inlineStr">
         <is>
-          <t>LEFT JOIN I.CHANGE_TYPE_CODE = H.CHANGE_TYPE_CODE AND I.DETAIL_CHANGE_TYPE_CODE = H.DETAIL_CHANGE_TYPE_CODE</t>
-        </is>
-      </c>
-    </row>
-    <row r="49" ht="15" customHeight="1">
+          <t>LEFT JOIN H.WI_NAME = A.WI_NAME</t>
+        </is>
+      </c>
+    </row>
+    <row r="49" ht="30" customHeight="1">
       <c r="A49" s="25" t="n"/>
       <c r="B49" s="25" t="n"/>
       <c r="C49" s="51" t="n"/>
       <c r="D49" s="54" t="n"/>
       <c r="E49" s="8" t="inlineStr">
         <is>
-          <t>LEFT JOIN J.WI_NAME = A.WI_NAME</t>
+          <t>LEFT JOIN I.CHANGE_TYPE_CODE = H.CHANGE_TYPE_CODE AND I.DETAIL_CHANGE_TYPE_CODE = H.DETAIL_CHANGE_TYPE_CODE</t>
         </is>
       </c>
     </row>
@@ -1619,7 +1635,7 @@
       <c r="D50" s="54" t="n"/>
       <c r="E50" s="8" t="inlineStr">
         <is>
-          <t>LEFT JOIN K.PROMOTION_CODE = J.PROMOTION_ID</t>
+          <t>LEFT JOIN J.WI_NAME = A.WI_NAME</t>
         </is>
       </c>
     </row>
@@ -1629,6 +1645,17 @@
       <c r="C51" s="51" t="n"/>
       <c r="D51" s="54" t="n"/>
       <c r="E51" s="8" t="inlineStr">
+        <is>
+          <t>LEFT JOIN K.PROMOTION_CODE = J.PROMOTION_ID</t>
+        </is>
+      </c>
+    </row>
+    <row r="52" ht="15" customHeight="1">
+      <c r="A52" s="25" t="n"/>
+      <c r="B52" s="25" t="n"/>
+      <c r="C52" s="51" t="n"/>
+      <c r="D52" s="54" t="n"/>
+      <c r="E52" s="8" t="inlineStr">
         <is>
           <t>LEFT JOIN L.WI_NAME = A.WI_NAME</t>
         </is>
